--- a/data/trans_dic/IP12-Clase-trans_dic.xlsx
+++ b/data/trans_dic/IP12-Clase-trans_dic.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variables dicotomizadas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Porcentajes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Totales" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -526,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que limitaron su actividad por dolores o síntomas</t>
+          <t>Menores que limitaron su actividad por dolores o síntomas (tasa de respuesta: 99,99%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -716,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>2,95; 9,46</t>
+          <t>2,6; 9,44</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>5,26; 16,22</t>
+          <t>5,04; 15,08</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>6,75; 18,64</t>
+          <t>6,61; 17,79</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>6,12; 16,29</t>
+          <t>6,26; 16,34</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>5,47; 15,5</t>
+          <t>5,35; 15,07</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>3,8; 13,28</t>
+          <t>3,43; 13,61</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>1,39; 8,04</t>
+          <t>1,32; 7,91</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>1,88; 8,71</t>
+          <t>1,76; 8,84</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>4,87; 10,8</t>
+          <t>4,96; 10,66</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>5,48; 12,51</t>
+          <t>5,44; 12,53</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>4,67; 11,33</t>
+          <t>4,7; 11,05</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>4,61; 10,57</t>
+          <t>4,63; 10,43</t>
         </is>
       </c>
     </row>
@@ -856,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>3,69; 13,07</t>
+          <t>3,58; 13,3</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>7,95; 19,24</t>
+          <t>8,08; 19,97</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1,95; 8,82</t>
+          <t>2,18; 8,87</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>2,01; 9,18</t>
+          <t>1,96; 9,4</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>3,46; 12,46</t>
+          <t>3,39; 12,75</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,64; 11,14</t>
+          <t>2,65; 11,11</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,25; 12,52</t>
+          <t>4,28; 12,51</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>5,99; 17,27</t>
+          <t>6,06; 17,57</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>4,51; 10,58</t>
+          <t>4,78; 11,14</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>6,27; 12,96</t>
+          <t>6,23; 13,19</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>4,19; 9,26</t>
+          <t>4,14; 9,14</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>5,05; 11,89</t>
+          <t>4,85; 11,5</t>
         </is>
       </c>
     </row>
@@ -996,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>2,84; 12,67</t>
+          <t>2,76; 12,68</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>4,61; 14,99</t>
+          <t>4,67; 14,91</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>3,23; 14,4</t>
+          <t>3,28; 14,88</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2,48; 12,51</t>
+          <t>2,54; 12,95</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>3,42; 11,77</t>
+          <t>3,54; 12,71</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>5,05; 15,57</t>
+          <t>5,0; 15,19</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>2,68; 12,88</t>
+          <t>2,49; 13,08</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>3,21; 15,31</t>
+          <t>3,41; 15,22</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>4,25; 10,68</t>
+          <t>4,13; 10,54</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>5,76; 12,92</t>
+          <t>5,85; 12,79</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>4,01; 11,42</t>
+          <t>3,91; 11,37</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>3,85; 11,43</t>
+          <t>3,74; 11,47</t>
         </is>
       </c>
     </row>
@@ -1136,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>4,36; 10,23</t>
+          <t>4,56; 10,21</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>5,47; 11,85</t>
+          <t>5,31; 11,96</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>6,36; 12,47</t>
+          <t>6,41; 12,5</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>2,46; 7,28</t>
+          <t>2,36; 7,42</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>5,16; 11,25</t>
+          <t>4,94; 10,99</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>6,7; 13,81</t>
+          <t>6,83; 13,98</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>5,36; 11,97</t>
+          <t>5,85; 12,15</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>4,36; 10,49</t>
+          <t>4,32; 10,35</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>5,27; 9,37</t>
+          <t>5,33; 9,55</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>6,99; 11,78</t>
+          <t>7,01; 11,81</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>6,71; 11,04</t>
+          <t>6,91; 10,99</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>3,89; 7,81</t>
+          <t>3,85; 7,77</t>
         </is>
       </c>
     </row>
@@ -1276,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>4,28; 13,7</t>
+          <t>4,36; 13,35</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>4,5; 11,98</t>
+          <t>4,8; 12,76</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>4,41; 11,66</t>
+          <t>4,61; 11,83</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>7,02; 16,75</t>
+          <t>7,4; 16,92</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>2,45; 8,38</t>
+          <t>2,44; 8,94</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3,71; 10,93</t>
+          <t>3,98; 11,2</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,42; 9,03</t>
+          <t>2,63; 8,51</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>5,62; 15,34</t>
+          <t>5,89; 15,89</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>3,95; 9,26</t>
+          <t>3,85; 9,27</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>5,07; 10,29</t>
+          <t>5,37; 10,33</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>4,18; 8,83</t>
+          <t>4,3; 9,03</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>7,26; 14,22</t>
+          <t>7,38; 14,02</t>
         </is>
       </c>
     </row>
@@ -1416,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>1,04; 9,03</t>
+          <t>0,9; 8,46</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1,41; 11,98</t>
+          <t>1,39; 11,58</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>2,0; 12,38</t>
+          <t>2,0; 11,72</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>3,02; 12,65</t>
+          <t>3,14; 12,84</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>2,55; 11,2</t>
+          <t>1,81; 10,63</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>4,42; 16,39</t>
+          <t>3,96; 15,47</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>2,07; 12,31</t>
+          <t>2,32; 11,9</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>2,06; 12,77</t>
+          <t>2,05; 12,46</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>2,55; 7,76</t>
+          <t>2,28; 8,03</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>4,01; 11,7</t>
+          <t>4,16; 12,31</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>2,93; 9,58</t>
+          <t>3,05; 10,54</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>3,66; 10,39</t>
+          <t>3,72; 10,5</t>
         </is>
       </c>
     </row>
@@ -1556,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>5,06; 8,15</t>
+          <t>4,98; 8,17</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>7,33; 10,89</t>
+          <t>7,23; 10,88</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>6,44; 9,65</t>
+          <t>6,38; 9,8</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>5,42; 8,73</t>
+          <t>5,53; 8,83</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>5,5; 8,66</t>
+          <t>5,5; 8,51</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>6,43; 9,92</t>
+          <t>6,57; 9,91</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>5,06; 8,17</t>
+          <t>5,08; 8,15</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>6,04; 9,57</t>
+          <t>5,91; 9,52</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>5,69; 7,88</t>
+          <t>5,64; 7,87</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>7,45; 9,98</t>
+          <t>7,5; 9,91</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>6,22; 8,47</t>
+          <t>6,18; 8,36</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>6,07; 8,49</t>
+          <t>6,2; 8,62</t>
         </is>
       </c>
     </row>
@@ -1638,4 +1639,1622 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:N25"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" min="14" max="14"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Menores que limitaron su actividad por dolores o síntomas (tasa de respuesta: 99,99%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="n"/>
+      <c r="E1" s="3" t="n"/>
+      <c r="F1" s="3" t="n"/>
+      <c r="G1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="H1" s="3" t="n"/>
+      <c r="I1" s="3" t="n"/>
+      <c r="J1" s="3" t="n"/>
+      <c r="K1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="L1" s="3" t="n"/>
+      <c r="M1" s="3" t="n"/>
+      <c r="N1" s="3" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="K2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="L2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="M2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="N2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+      <c r="F3" s="2" t="n"/>
+      <c r="G3" s="2" t="n"/>
+      <c r="H3" s="2" t="n"/>
+      <c r="I3" s="2" t="n"/>
+      <c r="J3" s="2" t="n"/>
+      <c r="K3" s="2" t="n"/>
+      <c r="L3" s="2" t="n"/>
+      <c r="M3" s="2" t="n"/>
+      <c r="N3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>Grupo I y II</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>5752</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>8636</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>9611</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>10930</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>9340</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>6613</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>3980</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>6329</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>15093</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>15249</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>13592</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>17258</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>2718; 9849</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>4537; 13559</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>5489; 14782</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>6540; 17065</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>5222; 14698</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>3079; 12217</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>1315; 7897</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>2406; 12103</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>10015; 21519</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>9769; 22514</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>8597; 20204</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>11177; 25166</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>Grupo III</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>6539</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>12137</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>5022</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>4398</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>6059</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>5585</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>8740</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>10285</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>12598</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>17722</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>13762</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>14682</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>3132; 11623</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>7533; 18626</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>2294; 9317</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>1853; 8897</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>2913; 10965</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>2566; 10754</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>4825; 14103</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>5792; 16792</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>8291; 19317</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>11834; 25068</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>9012; 19912</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>9223; 21881</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>Grupo IV y V</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>4362</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>7549</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>4532</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>3187</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>6868</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>7839</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>5031</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>4721</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>11230</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>15388</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>9563</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>7908</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>1860; 8544</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>4020; 12844</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>2029; 9202</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>1316; 6715</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>3517; 12622</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>4344; 13197</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>1875; 9869</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>2176; 9721</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>6883; 17577</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>10117; 22134</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>5362; 15604</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>4322; 13269</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Grupo VI</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>54</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>57</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>13828</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>17362</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>20552</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>9716</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>15304</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>22599</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>17502</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>15008</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>29132</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>39961</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>38054</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>24724</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>9163; 20492</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>10934; 24658</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>14330; 27953</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>5150; 16177</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>9981; 22200</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>15590; 31885</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>12341; 25611</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>9425; 22596</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>21484; 38459</t>
+        </is>
+      </c>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>30429; 51294</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>30035; 47733</t>
+        </is>
+      </c>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>16780; 33919</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>Grupo VII</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>8226</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>12093</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>10272</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>13451</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>6011</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>9604</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>7432</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>15714</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>14237</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>21697</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>17705</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>29165</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>4538; 13902</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>7159; 19028</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>6280; 16115</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>8835; 20202</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>3100; 11376</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>5608; 15799</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>3767; 12173</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>9574; 25842</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>8910; 21454</t>
+        </is>
+      </c>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>15599; 29989</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>12020; 25212</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
+        <is>
+          <t>20808; 39546</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>No ha trabajado</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="n"/>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>2769</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>2905</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>3406</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>4435</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>3810</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>6399</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>3886</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>4581</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>6579</t>
+        </is>
+      </c>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>9304</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>7292</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
+        <is>
+          <t>9017</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="n"/>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>670; 6332</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>750; 6244</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>1220; 7162</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>2161; 8844</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>1314; 7695</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>2932; 11451</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>1571; 8073</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
+          <t>1478; 8969</t>
+        </is>
+      </c>
+      <c r="K21" s="2" t="inlineStr">
+        <is>
+          <t>3356; 11830</t>
+        </is>
+      </c>
+      <c r="L21" s="2" t="inlineStr">
+        <is>
+          <t>5318; 15755</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="inlineStr">
+        <is>
+          <t>3929; 13581</t>
+        </is>
+      </c>
+      <c r="N21" s="2" t="inlineStr">
+        <is>
+          <t>5241; 14797</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>63</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>87</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>82</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>71</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>81</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>67</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>77</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>134</t>
+        </is>
+      </c>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>168</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>149</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
+        <is>
+          <t>152</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="n"/>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>41477</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>60683</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>53396</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>46117</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>47392</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>58638</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>46571</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>56638</t>
+        </is>
+      </c>
+      <c r="K23" s="2" t="inlineStr">
+        <is>
+          <t>88869</t>
+        </is>
+      </c>
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>119321</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>99966</t>
+        </is>
+      </c>
+      <c r="N23" s="2" t="inlineStr">
+        <is>
+          <t>102755</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="n"/>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>31834; 52207</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>49071; 73808</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>42780; 65769</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>36330; 58060</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>37631; 58274</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>47118; 71011</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>36089; 57835</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
+          <t>44244; 71301</t>
+        </is>
+      </c>
+      <c r="K24" s="2" t="inlineStr">
+        <is>
+          <t>74664; 104201</t>
+        </is>
+      </c>
+      <c r="L24" s="2" t="inlineStr">
+        <is>
+          <t>104576; 138196</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="inlineStr">
+        <is>
+          <t>85291; 115448</t>
+        </is>
+      </c>
+      <c r="N24" s="2" t="inlineStr">
+        <is>
+          <t>87223; 121286</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="11">
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="A19:A21"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="C1:F1"/>
+    <mergeCell ref="G1:J1"/>
+    <mergeCell ref="K1:N1"/>
+    <mergeCell ref="A22:A24"/>
+    <mergeCell ref="A13:A15"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/trans_dic/IP12-Clase-trans_dic.xlsx
+++ b/data/trans_dic/IP12-Clase-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que limitaron su actividad por dolores o síntomas (tasa de respuesta: 99,99%)</t>
+          <t>Menores que en las últimas 2 semanas limitaron su actividad por dolores o síntomas (tasa de respuesta: 99,99%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>2,6; 9,44</t>
+          <t>2,88; 10,19</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>5,04; 15,08</t>
+          <t>4,76; 15,13</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>6,61; 17,79</t>
+          <t>6,71; 18,15</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>6,26; 16,34</t>
+          <t>6,14; 16,35</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>5,35; 15,07</t>
+          <t>5,5; 15,19</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>3,43; 13,61</t>
+          <t>3,64; 13,67</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>1,32; 7,91</t>
+          <t>1,41; 8,06</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>1,76; 8,84</t>
+          <t>2,04; 8,94</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>4,96; 10,66</t>
+          <t>4,76; 10,82</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>5,44; 12,53</t>
+          <t>5,41; 12,8</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>4,7; 11,05</t>
+          <t>4,75; 11,14</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>4,63; 10,43</t>
+          <t>4,78; 10,97</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>3,58; 13,3</t>
+          <t>3,78; 13,12</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>8,08; 19,97</t>
+          <t>7,91; 19,37</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2,18; 8,87</t>
+          <t>2,2; 9,5</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>1,96; 9,4</t>
+          <t>1,99; 9,22</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>3,39; 12,75</t>
+          <t>3,3; 12,59</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,65; 11,11</t>
+          <t>2,72; 10,92</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,28; 12,51</t>
+          <t>4,14; 12,37</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>6,06; 17,57</t>
+          <t>5,8; 17,53</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>4,78; 11,14</t>
+          <t>4,29; 10,84</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>6,23; 13,19</t>
+          <t>6,16; 13,15</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>4,14; 9,14</t>
+          <t>4,03; 9,39</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>4,85; 11,5</t>
+          <t>4,82; 11,7</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>2,76; 12,68</t>
+          <t>2,79; 12,94</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>4,67; 14,91</t>
+          <t>4,73; 15,06</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>3,28; 14,88</t>
+          <t>3,1; 14,26</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2,54; 12,95</t>
+          <t>2,43; 13,1</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>3,54; 12,71</t>
+          <t>3,42; 12,42</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>5,0; 15,19</t>
+          <t>5,28; 15,33</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>2,49; 13,08</t>
+          <t>3,19; 13,54</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>3,41; 15,22</t>
+          <t>3,1; 14,44</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>4,13; 10,54</t>
+          <t>4,02; 10,52</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>5,85; 12,79</t>
+          <t>5,96; 13,4</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>3,91; 11,37</t>
+          <t>3,97; 11,09</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>3,74; 11,47</t>
+          <t>3,32; 11,51</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>4,56; 10,21</t>
+          <t>4,16; 9,85</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>5,31; 11,96</t>
+          <t>5,5; 11,98</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>6,41; 12,5</t>
+          <t>6,5; 12,63</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>2,36; 7,42</t>
+          <t>2,33; 7,51</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>4,94; 10,99</t>
+          <t>4,73; 10,66</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>6,83; 13,98</t>
+          <t>6,93; 13,62</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>5,85; 12,15</t>
+          <t>5,76; 11,98</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>4,32; 10,35</t>
+          <t>4,3; 10,75</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>5,33; 9,55</t>
+          <t>5,41; 9,65</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>7,01; 11,81</t>
+          <t>7,06; 11,86</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>6,91; 10,99</t>
+          <t>6,76; 11,47</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>3,85; 7,77</t>
+          <t>3,81; 7,78</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>4,36; 13,35</t>
+          <t>4,02; 12,98</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>4,8; 12,76</t>
+          <t>5,05; 12,71</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>4,61; 11,83</t>
+          <t>4,19; 11,92</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>7,4; 16,92</t>
+          <t>7,23; 16,52</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>2,44; 8,94</t>
+          <t>2,18; 8,36</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3,98; 11,2</t>
+          <t>3,97; 10,99</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,63; 8,51</t>
+          <t>2,84; 9,08</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>5,89; 15,89</t>
+          <t>5,71; 15,48</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>3,85; 9,27</t>
+          <t>3,71; 9,04</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>5,37; 10,33</t>
+          <t>5,28; 10,52</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>4,3; 9,03</t>
+          <t>4,39; 9,37</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>7,38; 14,02</t>
+          <t>7,31; 14,19</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0,9; 8,46</t>
+          <t>0,91; 9,25</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1,39; 11,58</t>
+          <t>1,49; 12,32</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>2,0; 11,72</t>
+          <t>2,11; 12,01</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>3,14; 12,84</t>
+          <t>2,9; 11,8</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>1,81; 10,63</t>
+          <t>1,79; 11,16</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>3,96; 15,47</t>
+          <t>4,29; 15,15</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>2,32; 11,9</t>
+          <t>1,9; 11,6</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>2,05; 12,46</t>
+          <t>2,57; 12,89</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>2,28; 8,03</t>
+          <t>2,21; 8,06</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>4,16; 12,31</t>
+          <t>3,88; 11,89</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>3,05; 10,54</t>
+          <t>2,8; 9,55</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>3,72; 10,5</t>
+          <t>3,23; 9,96</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>4,98; 8,17</t>
+          <t>5,08; 8,0</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>7,23; 10,88</t>
+          <t>7,28; 11,03</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>6,38; 9,8</t>
+          <t>6,18; 9,77</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>5,53; 8,83</t>
+          <t>5,41; 8,91</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>5,5; 8,51</t>
+          <t>5,53; 8,48</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>6,57; 9,91</t>
+          <t>6,56; 9,98</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>5,08; 8,15</t>
+          <t>5,01; 8,22</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>5,91; 9,52</t>
+          <t>5,83; 9,5</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>5,64; 7,87</t>
+          <t>5,67; 7,91</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>7,5; 9,91</t>
+          <t>7,27; 9,77</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>6,18; 8,36</t>
+          <t>6,06; 8,38</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>6,2; 8,62</t>
+          <t>6,05; 8,61</t>
         </is>
       </c>
     </row>
@@ -1669,7 +1669,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que limitaron su actividad por dolores o síntomas (tasa de respuesta: 99,99%)</t>
+          <t>Menores que en las últimas 2 semanas limitaron su actividad por dolores o síntomas (tasa de respuesta: 99,99%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1927,62 +1927,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>2718; 9849</t>
+          <t>3004; 10633</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>4537; 13559</t>
+          <t>4281; 13606</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>5489; 14782</t>
+          <t>5578; 15083</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>6540; 17065</t>
+          <t>6419; 17083</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>5222; 14698</t>
+          <t>5365; 14813</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>3079; 12217</t>
+          <t>3265; 12275</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>1315; 7897</t>
+          <t>1407; 8042</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>2406; 12103</t>
+          <t>2791; 12234</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>10015; 21519</t>
+          <t>9606; 21847</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>9769; 22514</t>
+          <t>9715; 23003</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>8597; 20204</t>
+          <t>8679; 20365</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>11177; 25166</t>
+          <t>11546; 26470</t>
         </is>
       </c>
     </row>
@@ -2135,62 +2135,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>3132; 11623</t>
+          <t>3302; 11464</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>7533; 18626</t>
+          <t>7380; 18067</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2294; 9317</t>
+          <t>2313; 9981</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1853; 8897</t>
+          <t>1882; 8729</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>2913; 10965</t>
+          <t>2838; 10823</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>2566; 10754</t>
+          <t>2635; 10568</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>4825; 14103</t>
+          <t>4671; 13952</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>5792; 16792</t>
+          <t>5543; 16753</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>8291; 19317</t>
+          <t>7444; 18790</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>11834; 25068</t>
+          <t>11703; 24994</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>9012; 19912</t>
+          <t>8777; 20464</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>9223; 21881</t>
+          <t>9165; 22260</t>
         </is>
       </c>
     </row>
@@ -2343,62 +2343,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>1860; 8544</t>
+          <t>1879; 8722</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>4020; 12844</t>
+          <t>4077; 12975</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>2029; 9202</t>
+          <t>1918; 8821</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>1316; 6715</t>
+          <t>1263; 6795</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>3517; 12622</t>
+          <t>3392; 12337</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>4344; 13197</t>
+          <t>4589; 13324</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>1875; 9869</t>
+          <t>2409; 10216</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>2176; 9721</t>
+          <t>1977; 9221</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>6883; 17577</t>
+          <t>6699; 17541</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>10117; 22134</t>
+          <t>10319; 23188</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>5362; 15604</t>
+          <t>5454; 15219</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>4322; 13269</t>
+          <t>3839; 13322</t>
         </is>
       </c>
     </row>
@@ -2551,62 +2551,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>9163; 20492</t>
+          <t>8344; 19763</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>10934; 24658</t>
+          <t>11341; 24702</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>14330; 27953</t>
+          <t>14526; 28230</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>5150; 16177</t>
+          <t>5085; 16366</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>9981; 22200</t>
+          <t>9563; 21550</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>15590; 31885</t>
+          <t>15803; 31059</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>12341; 25611</t>
+          <t>12141; 25262</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>9425; 22596</t>
+          <t>9384; 23458</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>21484; 38459</t>
+          <t>21802; 38889</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>30429; 51294</t>
+          <t>30652; 51519</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>30035; 47733</t>
+          <t>29379; 49851</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>16780; 33919</t>
+          <t>16629; 33925</t>
         </is>
       </c>
     </row>
@@ -2759,62 +2759,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>4538; 13902</t>
+          <t>4181; 13520</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>7159; 19028</t>
+          <t>7536; 18955</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>6280; 16115</t>
+          <t>5710; 16235</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>8835; 20202</t>
+          <t>8633; 19733</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>3100; 11376</t>
+          <t>2778; 10635</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>5608; 15799</t>
+          <t>5607; 15501</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>3767; 12173</t>
+          <t>4063; 12996</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>9574; 25842</t>
+          <t>9293; 25181</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>8910; 21454</t>
+          <t>8585; 20910</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>15599; 29989</t>
+          <t>15328; 30536</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>12020; 25212</t>
+          <t>12248; 26173</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>20808; 39546</t>
+          <t>20628; 40028</t>
         </is>
       </c>
     </row>
@@ -2967,62 +2967,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>670; 6332</t>
+          <t>680; 6928</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>750; 6244</t>
+          <t>804; 6643</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>1220; 7162</t>
+          <t>1287; 7337</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>2161; 8844</t>
+          <t>1999; 8132</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>1314; 7695</t>
+          <t>1297; 8076</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>2932; 11451</t>
+          <t>3178; 11216</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>1571; 8073</t>
+          <t>1290; 7865</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>1478; 8969</t>
+          <t>1847; 9279</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>3356; 11830</t>
+          <t>3253; 11863</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>5318; 15755</t>
+          <t>4958; 15214</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>3929; 13581</t>
+          <t>3615; 12310</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>5241; 14797</t>
+          <t>4558; 14040</t>
         </is>
       </c>
     </row>
@@ -3175,62 +3175,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>31834; 52207</t>
+          <t>32455; 51120</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>49071; 73808</t>
+          <t>49423; 74851</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>42780; 65769</t>
+          <t>41442; 65515</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>36330; 58060</t>
+          <t>35593; 58583</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>37631; 58274</t>
+          <t>37845; 58068</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>47118; 71011</t>
+          <t>46986; 71504</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>36089; 57835</t>
+          <t>35545; 58358</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>44244; 71301</t>
+          <t>43642; 71139</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>74664; 104201</t>
+          <t>75103; 104622</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>104576; 138196</t>
+          <t>101384; 136307</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>85291; 115448</t>
+          <t>83702; 115647</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>87223; 121286</t>
+          <t>85154; 121095</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IP12-Clase-trans_dic.xlsx
+++ b/data/trans_dic/IP12-Clase-trans_dic.xlsx
@@ -533,7 +533,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -541,7 +541,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -649,42 +649,42 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>9,58%</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>7,37%</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>3,99%</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>4,8%</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>5,51%</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>9,6%</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>11,57%</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>10,46%</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>9,58%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>7,37%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>3,99%</t>
-        </is>
-      </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>4,62%</t>
+          <t>10,98%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>7,15%</t>
+          <t>7,62%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>2,88; 10,19</t>
+          <t>5,47; 15,5</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>4,76; 15,13</t>
+          <t>3,8; 13,28</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>6,71; 18,15</t>
+          <t>1,39; 8,04</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>6,14; 16,35</t>
+          <t>1,95; 8,79</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>5,5; 15,19</t>
+          <t>2,95; 9,46</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>3,64; 13,67</t>
+          <t>5,26; 16,22</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>1,41; 8,06</t>
+          <t>6,75; 18,64</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>2,04; 8,94</t>
+          <t>6,61; 17,13</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>4,76; 10,82</t>
+          <t>4,87; 10,8</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>5,41; 12,8</t>
+          <t>5,48; 12,51</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>4,75; 11,14</t>
+          <t>4,67; 11,33</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>4,78; 10,97</t>
+          <t>4,92; 11,12</t>
         </is>
       </c>
     </row>
@@ -789,42 +789,42 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>7,05%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>5,77%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>7,75%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>11,23%</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
           <t>7,48%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>13,01%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="I6" s="2" t="inlineStr">
         <is>
           <t>4,78%</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>4,64%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>7,05%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>5,77%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>7,75%</t>
-        </is>
-      </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>10,76%</t>
+          <t>4,29%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>7,72%</t>
+          <t>7,66%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>3,78; 13,12</t>
+          <t>3,46; 12,46</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>7,91; 19,37</t>
+          <t>2,64; 11,14</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2,2; 9,5</t>
+          <t>4,25; 12,52</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>1,99; 9,22</t>
+          <t>6,19; 17,94</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>3,3; 12,59</t>
+          <t>3,69; 13,07</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,72; 10,92</t>
+          <t>7,95; 19,24</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,14; 12,37</t>
+          <t>1,95; 8,82</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>5,8; 17,53</t>
+          <t>1,83; 8,73</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>4,29; 10,84</t>
+          <t>4,51; 10,58</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>6,16; 13,15</t>
+          <t>6,27; 12,96</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>4,03; 9,39</t>
+          <t>4,19; 9,26</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>4,82; 11,7</t>
+          <t>5,04; 12,01</t>
         </is>
       </c>
     </row>
@@ -929,42 +929,42 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>6,91%</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>9,02%</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>6,67%</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>7,38%</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>6,47%</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>8,76%</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>7,33%</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>6,15%</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>6,91%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>9,02%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>6,67%</t>
-        </is>
-      </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>7,39%</t>
+          <t>5,56%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>6,83%</t>
+          <t>6,5%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>2,79; 12,94</t>
+          <t>3,42; 11,77</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>4,73; 15,06</t>
+          <t>5,05; 15,57</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>3,1; 14,26</t>
+          <t>2,68; 12,88</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2,43; 13,1</t>
+          <t>2,98; 15,27</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>3,42; 12,42</t>
+          <t>2,84; 12,67</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>5,28; 15,33</t>
+          <t>4,61; 14,99</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>3,19; 13,54</t>
+          <t>3,23; 14,4</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>3,1; 14,44</t>
+          <t>2,12; 11,61</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>4,02; 10,52</t>
+          <t>4,25; 10,68</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>5,96; 13,4</t>
+          <t>5,76; 12,92</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>3,97; 11,09</t>
+          <t>4,01; 11,42</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>3,32; 11,51</t>
+          <t>3,54; 11,38</t>
         </is>
       </c>
     </row>
@@ -1069,42 +1069,42 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>7,57%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>9,91%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>8,3%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>6,77%</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>6,89%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>8,42%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>9,19%</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>4,46%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>7,57%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>9,91%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>8,3%</t>
-        </is>
-      </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>6,88%</t>
+          <t>5,34%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>5,67%</t>
+          <t>6,09%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>4,16; 9,85</t>
+          <t>5,16; 11,25</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>5,5; 11,98</t>
+          <t>6,7; 13,81</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>6,5; 12,63</t>
+          <t>5,36; 11,97</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>2,33; 7,51</t>
+          <t>4,24; 10,29</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>4,73; 10,66</t>
+          <t>4,36; 10,23</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>6,93; 13,62</t>
+          <t>5,47; 11,85</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>5,76; 11,98</t>
+          <t>6,36; 12,47</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>4,3; 10,75</t>
+          <t>3,17; 8,63</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>5,41; 9,65</t>
+          <t>5,27; 9,37</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>7,06; 11,86</t>
+          <t>6,99; 11,78</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>6,76; 11,47</t>
+          <t>6,71; 11,04</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>3,81; 7,78</t>
+          <t>4,32; 8,51</t>
         </is>
       </c>
     </row>
@@ -1209,42 +1209,42 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>4,72%</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>6,81%</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>5,19%</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>9,9%</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
           <t>7,9%</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="H12" s="2" t="inlineStr">
         <is>
           <t>8,11%</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="I12" s="2" t="inlineStr">
         <is>
           <t>7,54%</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>11,26%</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>4,72%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>6,81%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>5,19%</t>
-        </is>
-      </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>9,66%</t>
+          <t>10,8%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>10,34%</t>
+          <t>10,3%</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>4,02; 12,98</t>
+          <t>2,45; 8,38</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>5,05; 12,71</t>
+          <t>3,71; 10,93</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>4,19; 11,92</t>
+          <t>2,42; 9,03</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>7,23; 16,52</t>
+          <t>5,8; 15,94</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>2,18; 8,36</t>
+          <t>4,28; 13,7</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3,97; 10,99</t>
+          <t>4,5; 11,98</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,84; 9,08</t>
+          <t>4,41; 11,66</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>5,71; 15,48</t>
+          <t>6,69; 16,21</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>3,71; 9,04</t>
+          <t>3,95; 9,26</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>5,28; 10,52</t>
+          <t>5,07; 10,29</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>4,39; 9,37</t>
+          <t>4,18; 8,83</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>7,31; 14,19</t>
+          <t>7,39; 14,6</t>
         </is>
       </c>
     </row>
@@ -1349,42 +1349,42 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>5,26%</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>8,64%</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>5,73%</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>6,79%</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
           <t>3,7%</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>5,39%</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="I14" s="2" t="inlineStr">
         <is>
           <t>5,58%</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>6,44%</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>5,26%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>8,64%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>5,73%</t>
-        </is>
-      </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>6,36%</t>
+          <t>6,67%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>6,4%</t>
+          <t>6,73%</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0,91; 9,25</t>
+          <t>2,55; 11,2</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1,49; 12,32</t>
+          <t>4,42; 16,39</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>2,11; 12,01</t>
+          <t>2,07; 12,31</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>2,9; 11,8</t>
+          <t>2,2; 13,77</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>1,79; 11,16</t>
+          <t>1,04; 9,03</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>4,29; 15,15</t>
+          <t>1,41; 11,98</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>1,9; 11,6</t>
+          <t>2,0; 12,38</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>2,57; 12,89</t>
+          <t>3,08; 13,34</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>2,21; 8,06</t>
+          <t>2,55; 7,76</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>3,88; 11,89</t>
+          <t>4,01; 11,7</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>2,8; 9,55</t>
+          <t>2,93; 9,58</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>3,23; 9,96</t>
+          <t>3,87; 10,93</t>
         </is>
       </c>
     </row>
@@ -1489,42 +1489,42 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>6,92%</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>8,18%</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>6,56%</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>7,74%</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
           <t>6,49%</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>8,94%</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="I16" s="2" t="inlineStr">
         <is>
           <t>7,96%</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>7,02%</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>6,92%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>8,18%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>6,56%</t>
-        </is>
-      </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>7,56%</t>
+          <t>7,33%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>7,31%</t>
+          <t>7,54%</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>5,08; 8,0</t>
+          <t>5,5; 8,66</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>7,28; 11,03</t>
+          <t>6,43; 9,92</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>6,18; 9,77</t>
+          <t>5,06; 8,17</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>5,41; 8,91</t>
+          <t>6,13; 9,8</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>5,53; 8,48</t>
+          <t>5,06; 8,15</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>6,56; 9,98</t>
+          <t>7,33; 10,89</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>5,01; 8,22</t>
+          <t>6,44; 9,65</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>5,83; 9,5</t>
+          <t>5,75; 9,05</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>5,67; 7,91</t>
+          <t>5,69; 7,88</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>7,27; 9,77</t>
+          <t>7,45; 9,98</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>6,06; 8,38</t>
+          <t>6,22; 8,47</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>6,05; 8,61</t>
+          <t>6,33; 8,75</t>
         </is>
       </c>
     </row>
@@ -1675,7 +1675,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -1683,7 +1683,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -1791,42 +1791,42 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>10</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>14</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="J4" s="2" t="inlineStr">
         <is>
           <t>17</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -1859,42 +1859,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>9340</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>6613</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>3980</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>5880</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
           <t>5752</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>8636</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="I5" s="2" t="inlineStr">
         <is>
           <t>9611</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>10930</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>9340</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>6613</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>3980</t>
-        </is>
-      </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>6329</t>
+          <t>11305</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1914,7 +1914,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>17258</t>
+          <t>17185</t>
         </is>
       </c>
     </row>
@@ -1927,62 +1927,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>3004; 10633</t>
+          <t>5336; 15123</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>4281; 13606</t>
+          <t>3409; 11920</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>5578; 15083</t>
+          <t>1383; 8023</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>6419; 17083</t>
+          <t>2393; 10777</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>5365; 14813</t>
+          <t>3074; 9876</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>3265; 12275</t>
+          <t>4726; 14584</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>1407; 8042</t>
+          <t>5606; 15485</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>2791; 12234</t>
+          <t>6806; 17630</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>9606; 21847</t>
+          <t>9837; 21798</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>9715; 23003</t>
+          <t>9850; 22487</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>8679; 20365</t>
+          <t>8536; 20722</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>11546; 26470</t>
+          <t>11101; 25077</t>
         </is>
       </c>
     </row>
@@ -1999,42 +1999,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
           <t>10</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>18</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="I7" s="2" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="J7" s="2" t="inlineStr">
         <is>
           <t>7</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>14</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -2067,42 +2067,42 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>6059</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>5585</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>8740</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>10267</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>6539</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>12137</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>5022</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>4398</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>6059</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>5585</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>8740</t>
-        </is>
-      </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>10285</t>
+          <t>4137</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -2122,7 +2122,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>14682</t>
+          <t>14404</t>
         </is>
       </c>
     </row>
@@ -2135,62 +2135,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>3302; 11464</t>
+          <t>2977; 10713</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>7380; 18067</t>
+          <t>2551; 10784</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2313; 9981</t>
+          <t>4790; 14116</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1882; 8729</t>
+          <t>5660; 16395</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>2838; 10823</t>
+          <t>3222; 11422</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>2635; 10568</t>
+          <t>7416; 17945</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>4671; 13952</t>
+          <t>2051; 9268</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>5543; 16753</t>
+          <t>1766; 8426</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>7444; 18790</t>
+          <t>7826; 18344</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>11703; 24994</t>
+          <t>11916; 24633</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>8777; 20464</t>
+          <t>9123; 20173</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>9165; 22260</t>
+          <t>9477; 22573</t>
         </is>
       </c>
     </row>
@@ -2207,42 +2207,42 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="J10" s="2" t="inlineStr">
         <is>
           <t>6</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -2275,42 +2275,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>6868</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>7839</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>5031</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>4205</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
           <t>4362</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="H11" s="2" t="inlineStr">
         <is>
           <t>7549</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="I11" s="2" t="inlineStr">
         <is>
           <t>4532</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>3187</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>6868</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>7839</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>5031</t>
-        </is>
-      </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>4721</t>
+          <t>2975</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2330,7 +2330,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>7908</t>
+          <t>7179</t>
         </is>
       </c>
     </row>
@@ -2343,62 +2343,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>1879; 8722</t>
+          <t>3393; 11689</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>4077; 12975</t>
+          <t>4387; 13526</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1918; 8821</t>
+          <t>2020; 9716</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>1263; 6795</t>
+          <t>1696; 8697</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>3392; 12337</t>
+          <t>1913; 8541</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>4589; 13324</t>
+          <t>3974; 12911</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>2409; 10216</t>
+          <t>2000; 8907</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>1977; 9221</t>
+          <t>1135; 6207</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>6699; 17541</t>
+          <t>7080; 17813</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>10319; 23188</t>
+          <t>9959; 22365</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>5454; 15219</t>
+          <t>5507; 15678</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>3839; 13322</t>
+          <t>3907; 12570</t>
         </is>
       </c>
     </row>
@@ -2415,42 +2415,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
           <t>21</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="H13" s="2" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="I13" s="2" t="inlineStr">
         <is>
           <t>32</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
+      <c r="J13" s="2" t="inlineStr">
         <is>
           <t>15</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>29</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>22</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
@@ -2483,42 +2483,42 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>15304</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>22599</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>17502</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>13662</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
           <t>13828</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>17362</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="I14" s="2" t="inlineStr">
         <is>
           <t>20552</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>9716</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>15304</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>22599</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>17502</t>
-        </is>
-      </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>15008</t>
+          <t>9543</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2538,7 +2538,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>24724</t>
+          <t>23206</t>
         </is>
       </c>
     </row>
@@ -2551,62 +2551,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>8344; 19763</t>
+          <t>10435; 22723</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>11341; 24702</t>
+          <t>15292; 31494</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>14526; 28230</t>
+          <t>11307; 25231</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>5085; 16366</t>
+          <t>8560; 20783</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>9563; 21550</t>
+          <t>8745; 20526</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>15803; 31059</t>
+          <t>11276; 24424</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>12141; 25262</t>
+          <t>14213; 27878</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>9384; 23458</t>
+          <t>5663; 15430</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>21802; 38889</t>
+          <t>21217; 37740</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>30652; 51519</t>
+          <t>30354; 51134</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>29379; 49851</t>
+          <t>29152; 47969</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>16629; 33925</t>
+          <t>16433; 32416</t>
         </is>
       </c>
     </row>
@@ -2623,42 +2623,42 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
           <t>11</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>17</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="I16" s="2" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
+      <c r="J16" s="2" t="inlineStr">
         <is>
           <t>22</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>20</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -2691,42 +2691,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>6011</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>9604</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>7432</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>14678</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
           <t>8226</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="H17" s="2" t="inlineStr">
         <is>
           <t>12093</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
+      <c r="I17" s="2" t="inlineStr">
         <is>
           <t>10272</t>
         </is>
       </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>13451</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>6011</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>9604</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>7432</t>
-        </is>
-      </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>15714</t>
+          <t>12827</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2746,7 +2746,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>29165</t>
+          <t>27505</t>
         </is>
       </c>
     </row>
@@ -2759,62 +2759,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>4181; 13520</t>
+          <t>3120; 10662</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>7536; 18955</t>
+          <t>5228; 15419</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>5710; 16235</t>
+          <t>3463; 12926</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>8633; 19733</t>
+          <t>8598; 23623</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>2778; 10635</t>
+          <t>4455; 14261</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>5607; 15501</t>
+          <t>6720; 17864</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>4063; 12996</t>
+          <t>6007; 15879</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>9293; 25181</t>
+          <t>7948; 19248</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>8585; 20910</t>
+          <t>9150; 21423</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>15328; 30536</t>
+          <t>14725; 29850</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>12248; 26173</t>
+          <t>11667; 24654</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>20628; 40028</t>
+          <t>19719; 38988</t>
         </is>
       </c>
     </row>
@@ -2831,42 +2831,42 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="H19" s="2" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
+      <c r="I19" s="2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="F19" s="2" t="inlineStr">
+      <c r="J19" s="2" t="inlineStr">
         <is>
           <t>8</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
@@ -2899,42 +2899,42 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>3810</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>6399</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>3886</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>4638</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
           <t>2769</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="H20" s="2" t="inlineStr">
         <is>
           <t>2905</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
+      <c r="I20" s="2" t="inlineStr">
         <is>
           <t>3406</t>
         </is>
       </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>4435</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>3810</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>6399</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>3886</t>
-        </is>
-      </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>4581</t>
+          <t>4694</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -2954,7 +2954,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>9017</t>
+          <t>9332</t>
         </is>
       </c>
     </row>
@@ -2967,62 +2967,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>680; 6928</t>
+          <t>1849; 8111</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>804; 6643</t>
+          <t>3274; 12133</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>1287; 7337</t>
+          <t>1403; 8351</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>1999; 8132</t>
+          <t>1501; 9402</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>1297; 8076</t>
+          <t>778; 6758</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>3178; 11216</t>
+          <t>758; 6457</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>1290; 7865</t>
+          <t>1222; 7563</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>1847; 9279</t>
+          <t>2166; 9387</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>3253; 11863</t>
+          <t>3761; 11431</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>4958; 15214</t>
+          <t>5131; 14964</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>3615; 12310</t>
+          <t>3782; 12354</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>4558; 14040</t>
+          <t>5360; 15152</t>
         </is>
       </c>
     </row>
@@ -3039,42 +3039,42 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>71</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>81</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>67</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>77</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
           <t>63</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="H22" s="2" t="inlineStr">
         <is>
           <t>87</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
+      <c r="I22" s="2" t="inlineStr">
         <is>
           <t>82</t>
         </is>
       </c>
-      <c r="F22" s="2" t="inlineStr">
+      <c r="J22" s="2" t="inlineStr">
         <is>
           <t>75</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>71</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>81</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>67</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>77</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
@@ -3107,42 +3107,42 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>47392</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>58638</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>46571</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>53330</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
           <t>41477</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="H23" s="2" t="inlineStr">
         <is>
           <t>60683</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
+      <c r="I23" s="2" t="inlineStr">
         <is>
           <t>53396</t>
         </is>
       </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>46117</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>47392</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>58638</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>46571</t>
-        </is>
-      </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>56638</t>
+          <t>45481</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -3162,7 +3162,7 @@
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>102755</t>
+          <t>98811</t>
         </is>
       </c>
     </row>
@@ -3175,62 +3175,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>32455; 51120</t>
+          <t>37635; 59306</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>49423; 74851</t>
+          <t>46050; 71074</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>41442; 65515</t>
+          <t>35892; 57972</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>35593; 58583</t>
+          <t>42281; 67574</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>37845; 58068</t>
+          <t>32318; 52040</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>46986; 71504</t>
+          <t>49734; 73927</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>35545; 58358</t>
+          <t>43224; 64744</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>43642; 71139</t>
+          <t>35723; 56170</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>75103; 104622</t>
+          <t>75345; 104341</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>101384; 136307</t>
+          <t>103909; 139173</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>83702; 115647</t>
+          <t>85844; 116942</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>85154; 121095</t>
+          <t>82905; 114644</t>
         </is>
       </c>
     </row>
